--- a/research/traditional_assets/database/data/estonia/estonia_food_processing.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_food_processing.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.03931133428981349</v>
+        <v>-0.09717868338557994</v>
       </c>
       <c r="H2">
-        <v>-0.03931133428981349</v>
+        <v>-0.09717868338557994</v>
       </c>
       <c r="I2">
-        <v>-0.05164992826398852</v>
+        <v>-0.1460815047021944</v>
       </c>
       <c r="J2">
-        <v>-0.05164992826398852</v>
+        <v>-0.1460815047021944</v>
       </c>
       <c r="K2">
-        <v>-5.27</v>
+        <v>-6.22</v>
       </c>
       <c r="L2">
-        <v>-0.07560975609756096</v>
+        <v>-0.1949843260188088</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.867</v>
+        <v>0.338</v>
       </c>
       <c r="V2">
-        <v>0.0562987012987013</v>
+        <v>0.02888888888888889</v>
       </c>
       <c r="W2">
-        <v>-0.2474178403755868</v>
+        <v>-0.376969696969697</v>
       </c>
       <c r="X2">
-        <v>0.1053874408569258</v>
+        <v>0.1519297041637289</v>
       </c>
       <c r="Y2">
-        <v>-0.3528052812325126</v>
+        <v>-0.5288994011334259</v>
       </c>
       <c r="Z2">
-        <v>2.321785476349101</v>
+        <v>1.150254209786175</v>
       </c>
       <c r="AA2">
-        <v>-0.1199200532978015</v>
+        <v>-0.168030865755598</v>
       </c>
       <c r="AB2">
-        <v>0.05194485506263144</v>
+        <v>0.08586036989622606</v>
       </c>
       <c r="AC2">
-        <v>-0.1718649083604329</v>
+        <v>-0.2538912356518241</v>
       </c>
       <c r="AD2">
-        <v>28.9</v>
+        <v>18.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>28.9</v>
+        <v>18.8</v>
       </c>
       <c r="AG2">
-        <v>28.033</v>
+        <v>18.462</v>
       </c>
       <c r="AH2">
-        <v>0.6523702031602709</v>
+        <v>0.6163934426229508</v>
       </c>
       <c r="AI2">
-        <v>0.6255411255411255</v>
+        <v>0.7059707097258731</v>
       </c>
       <c r="AJ2">
-        <v>0.6454308935601961</v>
+        <v>0.6120946886811219</v>
       </c>
       <c r="AK2">
-        <v>0.6183795469084331</v>
+        <v>0.7021907804655408</v>
       </c>
       <c r="AL2">
-        <v>0.837</v>
+        <v>1.49</v>
       </c>
       <c r="AM2">
-        <v>0.837</v>
+        <v>-0.1699999999999999</v>
       </c>
       <c r="AN2">
-        <v>-23.49593495934959</v>
+        <v>-5.714285714285714</v>
       </c>
       <c r="AO2">
-        <v>-4.301075268817205</v>
+        <v>-3.12751677852349</v>
       </c>
       <c r="AP2">
-        <v>-22.7910569105691</v>
+        <v>-5.611550151975684</v>
       </c>
       <c r="AQ2">
-        <v>-4.301075268817205</v>
+        <v>27.41176470588237</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.03931133428981349</v>
+        <v>-0.09717868338557994</v>
       </c>
       <c r="H3">
-        <v>-0.03931133428981349</v>
+        <v>-0.09717868338557994</v>
       </c>
       <c r="I3">
-        <v>-0.05164992826398852</v>
+        <v>-0.1460815047021944</v>
       </c>
       <c r="J3">
-        <v>-0.05164992826398852</v>
+        <v>-0.1460815047021944</v>
       </c>
       <c r="K3">
-        <v>-5.27</v>
+        <v>-6.22</v>
       </c>
       <c r="L3">
-        <v>-0.07560975609756096</v>
+        <v>-0.1949843260188088</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.867</v>
+        <v>0.338</v>
       </c>
       <c r="V3">
-        <v>0.0562987012987013</v>
+        <v>0.02888888888888889</v>
       </c>
       <c r="W3">
-        <v>-0.2474178403755868</v>
+        <v>-0.376969696969697</v>
       </c>
       <c r="X3">
-        <v>0.1053874408569258</v>
+        <v>0.1519297041637289</v>
       </c>
       <c r="Y3">
-        <v>-0.3528052812325126</v>
+        <v>-0.5288994011334259</v>
       </c>
       <c r="Z3">
-        <v>2.321785476349101</v>
+        <v>1.150254209786175</v>
       </c>
       <c r="AA3">
-        <v>-0.1199200532978015</v>
+        <v>-0.168030865755598</v>
       </c>
       <c r="AB3">
-        <v>0.05194485506263144</v>
+        <v>0.08586036989622606</v>
       </c>
       <c r="AC3">
-        <v>-0.1718649083604329</v>
+        <v>-0.2538912356518241</v>
       </c>
       <c r="AD3">
-        <v>28.9</v>
+        <v>18.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>28.9</v>
+        <v>18.8</v>
       </c>
       <c r="AG3">
-        <v>28.033</v>
+        <v>18.462</v>
       </c>
       <c r="AH3">
-        <v>0.6523702031602709</v>
+        <v>0.6163934426229508</v>
       </c>
       <c r="AI3">
-        <v>0.6255411255411255</v>
+        <v>0.7059707097258731</v>
       </c>
       <c r="AJ3">
-        <v>0.6454308935601961</v>
+        <v>0.6120946886811219</v>
       </c>
       <c r="AK3">
-        <v>0.6183795469084331</v>
+        <v>0.7021907804655408</v>
       </c>
       <c r="AL3">
-        <v>0.837</v>
+        <v>1.49</v>
       </c>
       <c r="AM3">
-        <v>0.837</v>
+        <v>-0.1699999999999999</v>
       </c>
       <c r="AN3">
-        <v>-23.49593495934959</v>
+        <v>-5.714285714285714</v>
       </c>
       <c r="AO3">
-        <v>-4.301075268817205</v>
+        <v>-3.12751677852349</v>
       </c>
       <c r="AP3">
-        <v>-22.7910569105691</v>
+        <v>-5.611550151975684</v>
       </c>
       <c r="AQ3">
-        <v>-4.301075268817205</v>
+        <v>27.41176470588237</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/estonia/estonia_food_processing.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_food_processing.xlsx
@@ -587,23 +587,26 @@
           <t>Food Processing</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.256</v>
+      </c>
       <c r="G2">
-        <v>-0.09717868338557994</v>
+        <v>0.01482051282051282</v>
       </c>
       <c r="H2">
-        <v>-0.09717868338557994</v>
+        <v>0.01482051282051282</v>
       </c>
       <c r="I2">
-        <v>-0.1460815047021944</v>
+        <v>-0.02964102564102564</v>
       </c>
       <c r="J2">
-        <v>-0.1460815047021944</v>
+        <v>-0.02964102564102564</v>
       </c>
       <c r="K2">
-        <v>-6.22</v>
+        <v>-1.32</v>
       </c>
       <c r="L2">
-        <v>-0.1949843260188088</v>
+        <v>-0.06769230769230769</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.338</v>
+        <v>0.211</v>
       </c>
       <c r="V2">
-        <v>0.02888888888888889</v>
+        <v>0.02828418230563003</v>
       </c>
       <c r="W2">
-        <v>-0.376969696969697</v>
+        <v>-0.1734559789750328</v>
       </c>
       <c r="X2">
-        <v>0.1519297041637289</v>
+        <v>0.1411633323820299</v>
       </c>
       <c r="Y2">
-        <v>-0.5288994011334259</v>
+        <v>-0.3146193113570628</v>
       </c>
       <c r="Z2">
-        <v>1.150254209786175</v>
+        <v>0.7479288125191776</v>
       </c>
       <c r="AA2">
-        <v>-0.168030865755598</v>
+        <v>-0.0221693771095428</v>
       </c>
       <c r="AB2">
-        <v>0.08586036989622606</v>
+        <v>0.07095730187068901</v>
       </c>
       <c r="AC2">
-        <v>-0.2538912356518241</v>
+        <v>-0.0931266789802318</v>
       </c>
       <c r="AD2">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="AG2">
-        <v>18.462</v>
+        <v>17.989</v>
       </c>
       <c r="AH2">
-        <v>0.6163934426229508</v>
+        <v>0.7092751363990647</v>
       </c>
       <c r="AI2">
-        <v>0.7059707097258731</v>
+        <v>0.6997308727412533</v>
       </c>
       <c r="AJ2">
-        <v>0.6120946886811219</v>
+        <v>0.7068647098117804</v>
       </c>
       <c r="AK2">
-        <v>0.7021907804655408</v>
+        <v>0.6972750881817125</v>
       </c>
       <c r="AL2">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AM2">
-        <v>-0.1699999999999999</v>
+        <v>1.609</v>
       </c>
       <c r="AN2">
-        <v>-5.714285714285714</v>
+        <v>30.18242122719735</v>
       </c>
       <c r="AO2">
-        <v>-3.12751677852349</v>
+        <v>-0.3590062111801242</v>
       </c>
       <c r="AP2">
-        <v>-5.611550151975684</v>
+        <v>29.83250414593698</v>
       </c>
       <c r="AQ2">
-        <v>27.41176470588237</v>
+        <v>-0.3592293349906774</v>
       </c>
     </row>
     <row r="3">
@@ -712,23 +715,26 @@
           <t>Food Processing</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.256</v>
+      </c>
       <c r="G3">
-        <v>-0.09717868338557994</v>
+        <v>0.01482051282051282</v>
       </c>
       <c r="H3">
-        <v>-0.09717868338557994</v>
+        <v>0.01482051282051282</v>
       </c>
       <c r="I3">
-        <v>-0.1460815047021944</v>
+        <v>-0.02964102564102564</v>
       </c>
       <c r="J3">
-        <v>-0.1460815047021944</v>
+        <v>-0.02964102564102564</v>
       </c>
       <c r="K3">
-        <v>-6.22</v>
+        <v>-1.32</v>
       </c>
       <c r="L3">
-        <v>-0.1949843260188088</v>
+        <v>-0.06769230769230769</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.338</v>
+        <v>0.211</v>
       </c>
       <c r="V3">
-        <v>0.02888888888888889</v>
+        <v>0.02828418230563003</v>
       </c>
       <c r="W3">
-        <v>-0.376969696969697</v>
+        <v>-0.1734559789750328</v>
       </c>
       <c r="X3">
-        <v>0.1519297041637289</v>
+        <v>0.1411633323820299</v>
       </c>
       <c r="Y3">
-        <v>-0.5288994011334259</v>
+        <v>-0.3146193113570628</v>
       </c>
       <c r="Z3">
-        <v>1.150254209786175</v>
+        <v>0.7479288125191776</v>
       </c>
       <c r="AA3">
-        <v>-0.168030865755598</v>
+        <v>-0.0221693771095428</v>
       </c>
       <c r="AB3">
-        <v>0.08586036989622606</v>
+        <v>0.07095730187068901</v>
       </c>
       <c r="AC3">
-        <v>-0.2538912356518241</v>
+        <v>-0.0931266789802318</v>
       </c>
       <c r="AD3">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="AG3">
-        <v>18.462</v>
+        <v>17.989</v>
       </c>
       <c r="AH3">
-        <v>0.6163934426229508</v>
+        <v>0.7092751363990647</v>
       </c>
       <c r="AI3">
-        <v>0.7059707097258731</v>
+        <v>0.6997308727412533</v>
       </c>
       <c r="AJ3">
-        <v>0.6120946886811219</v>
+        <v>0.7068647098117804</v>
       </c>
       <c r="AK3">
-        <v>0.7021907804655408</v>
+        <v>0.6972750881817125</v>
       </c>
       <c r="AL3">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AM3">
-        <v>-0.1699999999999999</v>
+        <v>1.609</v>
       </c>
       <c r="AN3">
-        <v>-5.714285714285714</v>
+        <v>30.18242122719735</v>
       </c>
       <c r="AO3">
-        <v>-3.12751677852349</v>
+        <v>-0.3590062111801242</v>
       </c>
       <c r="AP3">
-        <v>-5.611550151975684</v>
+        <v>29.83250414593698</v>
       </c>
       <c r="AQ3">
-        <v>27.41176470588237</v>
+        <v>-0.3592293349906774</v>
       </c>
     </row>
   </sheetData>
